--- a/registration_forms/040_finance_professionals_membership_form--registration_forms.xlsx
+++ b/registration_forms/040_finance_professionals_membership_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>financial_manager</t>
+          <t>financial_specialist</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial Manager</t>
+          <t>Financial Specialist</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>financial_specialist</t>
+          <t>financial_professional</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Specialist</t>
+          <t>Financial Professional</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>financial_professional</t>
+          <t>financial_director</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financial Professional</t>
+          <t>Financial Director</t>
         </is>
       </c>
     </row>
@@ -1284,63 +1284,63 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>financial_director</t>
+          <t>financial_expert</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financial Director</t>
+          <t>Financial Expert</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>membership_level_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>financial_manager</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financial Manager</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>membership_level_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>financial_advisor</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financial Advisor</t>
+          <t>Associate</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>membership_level_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>financial_expert</t>
+          <t>full_member</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financial Expert</t>
+          <t>Full Member</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>member</t>
+          <t>honorary_member</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Honorary Member</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>lifetime_member</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Lifetime Member</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>full_member</t>
+          <t>honorable</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Full Member</t>
+          <t>Honorable</t>
         </is>
       </c>
     </row>
@@ -1403,97 +1403,97 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>honorary_member</t>
+          <t>ordinary_member</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Honorary Member</t>
+          <t>Ordinary Member</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>membership_level_choices</t>
+          <t>company_size_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lifetime_member</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lifetime Member</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>membership_level_choices</t>
+          <t>company_size_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>honorable</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Honorable</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>membership_level_choices</t>
+          <t>company_sector_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ordinary_member</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ordinary Member</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>company_size_choices</t>
+          <t>company_sector_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>banking</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Banking</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>company_size_choices</t>
+          <t>company_sector_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>financial_services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>banking</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Accounting</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>auditing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Auditing</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>financial_services</t>
+          <t>taxation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Taxation</t>
         </is>
       </c>
     </row>
@@ -1573,61 +1573,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>accounting</t>
+          <t>financial_planning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Accounting</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>company_sector_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>auditing</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Auditing</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>company_sector_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>taxation</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Taxation</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>company_sector_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>financial_planning</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Financial Planning</t>
         </is>
